--- a/app/Archivos/Remittance/Remittance_farmatodo.xlsx
+++ b/app/Archivos/Remittance/Remittance_farmatodo.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael.Moreno\OneDrive - Unilever\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose-Ricardo.Morales\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B7BE000-4382-4426-B2FA-4537C333BF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{054ECFC4-7BD4-4BE0-A8C1-0D4A55F2CF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{591B3E77-5C04-4451-A3D3-B480B883E072}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B7AE75B-2B70-4199-BC30-4D3FD27995FF}"/>
   </bookViews>
   <sheets>
-    <sheet name="o17277106 (2)" sheetId="3" r:id="rId1"/>
+    <sheet name="o17511397" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" concurrentManualCount="12"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>FARMATODO COLOMBIA, S.A.</t>
   </si>
@@ -74,6 +61,9 @@
     <t>PROSEGUR</t>
   </si>
   <si>
+    <t>‭17-SEP-2025‬</t>
+  </si>
+  <si>
     <t>COP</t>
   </si>
   <si>
@@ -110,115 +100,43 @@
     <t>Total</t>
   </si>
   <si>
+    <t>‭PMP1279547‬</t>
+  </si>
+  <si>
+    <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1279547‬</t>
+  </si>
+  <si>
+    <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1279567‬</t>
+  </si>
+  <si>
+    <t>OC:14007453 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+  </si>
+  <si>
+    <t>‭PMP1279567‬</t>
+  </si>
+  <si>
+    <t>OC:14007453 UNILEVER ANDINA COLOMBIA LTDA</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1279890‬</t>
+  </si>
+  <si>
+    <t>OC:14007449 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+  </si>
+  <si>
+    <t>‭PMP1279890‬</t>
+  </si>
+  <si>
+    <t>OC:14007449 UNILEVER ANDINA COLOMBIA LTDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">                     </t>
-  </si>
-  <si>
-    <t>FV-XKZV26513</t>
-  </si>
-  <si>
-    <t>FV-XKZV27008</t>
-  </si>
-  <si>
-    <t>NC-DC04-755509</t>
-  </si>
-  <si>
-    <t>NC-DC04-755511</t>
-  </si>
-  <si>
-    <t>NC-DC04-755512</t>
-  </si>
-  <si>
-    <t>NC-DC04-755513</t>
-  </si>
-  <si>
-    <t>NC-DC04-755515</t>
-  </si>
-  <si>
-    <t>NC-DC04-755517</t>
-  </si>
-  <si>
-    <t>NC-DC04-755521</t>
-  </si>
-  <si>
-    <t>NC-DC04-755523</t>
-  </si>
-  <si>
-    <t>NC-DC04-755525</t>
-  </si>
-  <si>
-    <t>NC100320204</t>
-  </si>
-  <si>
-    <t>NCF-DC05-16088</t>
-  </si>
-  <si>
-    <t>PMP1254823</t>
-  </si>
-  <si>
-    <t>PMP1257523</t>
-  </si>
-  <si>
-    <t>PMP1257525</t>
-  </si>
-  <si>
-    <t>PMP1257526</t>
-  </si>
-  <si>
-    <t>Acuerdo Fijo Mensual 01 7%� - MASIVOS/MISCELANEOS Exhibiciones Adicionales</t>
-  </si>
-  <si>
-    <t>Cobro Descuento Apoyo Apertura mes de Junio-2025 Masivos Sucursal</t>
-  </si>
-  <si>
-    <t>Liquidaciones Ventas Pos -Primera Compra Junio - Belleza y cuidado personal</t>
-  </si>
-  <si>
-    <t>Liquidaciones ventas pos junio - Primaton</t>
-  </si>
-  <si>
-    <t>Liquidaciones Ventas Pos -Descuento Feria 12 al 15 Junio - Belleza y cuidado personal</t>
-  </si>
-  <si>
-    <t>Liquidaciones Ventas Pos -Combos Virtuales Junio - Belleza y cuidado personal</t>
-  </si>
-  <si>
-    <t>Liquidaciones ventas pos junio - Folleto 23 a 5</t>
-  </si>
-  <si>
-    <t>Liquidaciones ventas pos junio - Dcto Feria General</t>
-  </si>
-  <si>
-    <t>Liquidaciones Ventas Pos -Folleto Quincenal 6 al 19 Junio - Belleza y cuidado personal</t>
-  </si>
-  <si>
-    <t>Liquidaciones Ventas Pos -72 Horas 13 al 15 Junio - Belleza y cuidado personal</t>
-  </si>
-  <si>
-    <t>NOTAS DE CREDITO POR DEVOLUCION 100320204</t>
-  </si>
-  <si>
-    <t>Confidencial Acuerdo Fijo Mensual .4% 01-06-2025-30-06-20</t>
-  </si>
-  <si>
-    <t>OC:14002465 UNILEVER ANDINA COLOMBIA LTDA</t>
-  </si>
-  <si>
-    <t>OC:14002950 UNILEVER ANDINA COLOMBIA LTDA</t>
-  </si>
-  <si>
-    <t>OC:14002954 UNILEVER ANDINA COLOMBIA LTDA</t>
-  </si>
-  <si>
-    <t>OC:14004661 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
-  </si>
-  <si>
-    <t>NC-PMP1257523</t>
-  </si>
-  <si>
-    <t>NC-PMP1257525</t>
-  </si>
-  <si>
-    <t>NC-PMP1257526</t>
   </si>
 </sst>
 </file>
@@ -580,7 +498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -781,19 +699,6 @@
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -893,80 +798,80 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="18" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -982,7 +887,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1297,43 +1202,43 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE98506-CEA6-4EEE-A7BB-111A9CF742C0}">
-  <dimension ref="A1:O29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B890F33-5057-4BCE-BF60-B41F54772D10}">
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" customWidth="1"/>
-    <col min="5" max="5" width="13.90625" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" customWidth="1"/>
-    <col min="8" max="8" width="44.54296875" customWidth="1"/>
-    <col min="9" max="9" width="23.6328125" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" customWidth="1"/>
-    <col min="11" max="11" width="14.90625" customWidth="1"/>
-    <col min="12" max="12" width="21.7265625" customWidth="1"/>
-    <col min="13" max="13" width="27.1796875" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" customWidth="1"/>
-    <col min="15" max="15" width="16.36328125" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" customWidth="1"/>
+    <col min="13" max="13" width="28.77734375" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,59 +1265,59 @@
       <c r="N6" s="15"/>
       <c r="O6" s="16"/>
     </row>
-    <row r="7" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="17">
-        <v>10000061418</v>
-      </c>
-      <c r="C7" s="21">
-        <v>45866</v>
-      </c>
-      <c r="D7" s="25">
-        <v>44415234</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="B7" s="20">
+        <v>35172</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
+      <c r="D7" s="23">
+        <v>218819138.28</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>10</v>
+      </c>
       <c r="F7" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="18"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -1423,29 +1328,29 @@
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="18"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="21"/>
       <c r="F9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="8">
-        <v>45842</v>
+        <v>45895</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I9" s="10">
-        <v>-811023.46</v>
+        <v>105934733.18000001</v>
       </c>
       <c r="J9" s="10">
-        <v>0</v>
+        <v>20127599.300000001</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
@@ -1460,26 +1365,26 @@
         <v>0</v>
       </c>
       <c r="O9" s="10">
-        <v>-811023.46</v>
+        <v>126062332.48</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="18"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="21"/>
       <c r="F10" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="8">
-        <v>45842</v>
+        <v>45895</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I10" s="11">
-        <v>-15470000</v>
+        <v>0</v>
       </c>
       <c r="J10" s="11">
         <v>0</v>
@@ -1491,32 +1396,32 @@
         <v>0</v>
       </c>
       <c r="M10" s="10">
-        <v>0</v>
+        <v>-2118694.66</v>
       </c>
       <c r="N10" s="11">
         <v>0</v>
       </c>
       <c r="O10" s="10">
-        <v>-15470000</v>
+        <v>-2118694.66</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="18"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G11" s="8">
-        <v>45842</v>
+        <v>45895</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I11" s="11">
-        <v>-36331344.799999997</v>
+        <v>0</v>
       </c>
       <c r="J11" s="11">
         <v>0</v>
@@ -1528,35 +1433,35 @@
         <v>0</v>
       </c>
       <c r="M11" s="10">
-        <v>0</v>
+        <v>-1565497.97</v>
       </c>
       <c r="N11" s="11">
         <v>0</v>
       </c>
       <c r="O11" s="10">
-        <v>-36331344.799999997</v>
+        <v>-1565497.97</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="18"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G12" s="8">
-        <v>45842</v>
+        <v>45895</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="I12" s="10">
-        <v>-15374384.449999999</v>
+        <v>78274898.359999999</v>
       </c>
       <c r="J12" s="10">
-        <v>0</v>
+        <v>14872230.689999999</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -1571,28 +1476,28 @@
         <v>0</v>
       </c>
       <c r="O12" s="10">
-        <v>-15374384.449999999</v>
+        <v>93147129.049999997</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="18"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="21"/>
       <c r="F13" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G13" s="8">
-        <v>45842</v>
+        <v>45896</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="10">
-        <v>-13029314.1</v>
-      </c>
-      <c r="J13" s="10">
+        <v>31</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11">
         <v>0</v>
       </c>
       <c r="K13" s="11">
@@ -1601,36 +1506,36 @@
       <c r="L13" s="11">
         <v>0</v>
       </c>
-      <c r="M13" s="11">
-        <v>0</v>
+      <c r="M13" s="10">
+        <v>-50437.48</v>
       </c>
       <c r="N13" s="11">
         <v>0</v>
       </c>
       <c r="O13" s="10">
-        <v>-13029314.1</v>
+        <v>-50437.48</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="18"/>
+    <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="19"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G14" s="8">
-        <v>45842</v>
+        <v>45896</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I14" s="10">
-        <v>-8138292.1200000001</v>
+        <v>2865150.8</v>
       </c>
       <c r="J14" s="10">
-        <v>0</v>
+        <v>479156.06</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -1638,566 +1543,53 @@
       <c r="L14" s="11">
         <v>0</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="11">
         <v>0</v>
       </c>
       <c r="N14" s="11">
         <v>0</v>
       </c>
       <c r="O14" s="10">
-        <v>-8138292.1200000001</v>
+        <v>3344306.86</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="8">
-        <v>45842</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="10">
-        <v>-1563430</v>
-      </c>
-      <c r="J15" s="10">
-        <v>0</v>
-      </c>
-      <c r="K15" s="11">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11">
-        <v>0</v>
-      </c>
-      <c r="M15" s="10">
-        <v>0</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10">
-        <v>-1563430</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="8">
-        <v>45842</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="10">
-        <v>-964465.5</v>
-      </c>
-      <c r="J16" s="10">
-        <v>0</v>
-      </c>
-      <c r="K16" s="11">
-        <v>0</v>
-      </c>
-      <c r="L16" s="11">
-        <v>0</v>
-      </c>
-      <c r="M16" s="11">
-        <v>0</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0</v>
-      </c>
-      <c r="O16" s="10">
-        <v>-964465.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="8">
-        <v>45842</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="10">
-        <v>-2473742.2999999998</v>
-      </c>
-      <c r="J17" s="10">
-        <v>0</v>
-      </c>
-      <c r="K17" s="11">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11">
-        <v>0</v>
-      </c>
-      <c r="M17" s="10">
-        <v>0</v>
-      </c>
-      <c r="N17" s="11">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10">
-        <v>-2473742.2999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="8">
-        <v>45842</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="10">
-        <v>-1183970.05</v>
-      </c>
-      <c r="J18" s="10">
-        <v>0</v>
-      </c>
-      <c r="K18" s="11">
-        <v>0</v>
-      </c>
-      <c r="L18" s="11">
-        <v>0</v>
-      </c>
-      <c r="M18" s="11">
-        <v>0</v>
-      </c>
-      <c r="N18" s="11">
-        <v>0</v>
-      </c>
-      <c r="O18" s="10">
-        <v>-1183970.05</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="8">
-        <v>45842</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I19" s="10">
-        <v>-165487</v>
-      </c>
-      <c r="J19" s="10">
-        <v>0</v>
-      </c>
-      <c r="K19" s="11">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11">
-        <v>0</v>
-      </c>
-      <c r="M19" s="10">
-        <v>0</v>
-      </c>
-      <c r="N19" s="11">
-        <v>0</v>
-      </c>
-      <c r="O19" s="10">
-        <v>-165487</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="8">
-        <v>45859</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="10">
-        <v>-1250194.6299999999</v>
-      </c>
-      <c r="J20" s="10">
-        <v>-237536.98</v>
-      </c>
-      <c r="K20" s="11">
-        <v>0</v>
-      </c>
-      <c r="L20" s="11">
-        <v>0</v>
-      </c>
-      <c r="M20" s="11">
-        <v>0</v>
-      </c>
-      <c r="N20" s="11">
-        <v>0</v>
-      </c>
-      <c r="O20" s="10">
-        <v>-1487731.61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="5" t="s">
+    <row r="18" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="8">
-        <v>45840</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="10">
-        <v>-13948980.1</v>
-      </c>
-      <c r="J21" s="10">
-        <v>0</v>
-      </c>
-      <c r="K21" s="11">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11">
-        <v>0</v>
-      </c>
-      <c r="N21" s="11">
-        <v>0</v>
-      </c>
-      <c r="O21" s="10">
-        <v>-13948980.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="8">
-        <v>45830</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22" s="10">
-        <v>101600994.42</v>
-      </c>
-      <c r="J22" s="10">
-        <v>19304188.940000001</v>
-      </c>
-      <c r="K22" s="11">
-        <v>0</v>
-      </c>
-      <c r="L22" s="11">
-        <v>0</v>
-      </c>
-      <c r="M22" s="10">
-        <v>0</v>
-      </c>
-      <c r="N22" s="11">
-        <v>0</v>
-      </c>
-      <c r="O22" s="10">
-        <v>120905183.36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="8">
-        <v>45837</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I23" s="10">
-        <v>18524835.52</v>
-      </c>
-      <c r="J23" s="10">
-        <v>3519718.75</v>
-      </c>
-      <c r="K23" s="11">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11">
-        <v>0</v>
-      </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="11">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10">
-        <f>+I23+J23</f>
-        <v>22044554.27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24" s="8">
-        <v>45837</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="10">
-        <v>0</v>
-      </c>
-      <c r="J24" s="10">
-        <v>0</v>
-      </c>
-      <c r="K24" s="11">
-        <v>0</v>
-      </c>
-      <c r="L24" s="11">
-        <v>0</v>
-      </c>
-      <c r="M24" s="10">
-        <v>-370496.710420168</v>
-      </c>
-      <c r="N24" s="11">
-        <v>0</v>
-      </c>
-      <c r="O24" s="10">
-        <v>-370496.710420168</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="8">
-        <v>45837</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I25" s="10">
-        <v>3414076.44</v>
-      </c>
-      <c r="J25" s="10">
-        <v>648674.52</v>
-      </c>
-      <c r="K25" s="11">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11">
-        <v>0</v>
-      </c>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11">
-        <v>0</v>
-      </c>
-      <c r="O25" s="10">
-        <v>4062750.96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G26" s="8">
-        <v>45837</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I26" s="10">
-        <v>0</v>
-      </c>
-      <c r="J26" s="10">
-        <v>0</v>
-      </c>
-      <c r="K26" s="11">
-        <v>0</v>
-      </c>
-      <c r="L26" s="11">
-        <v>0</v>
-      </c>
-      <c r="M26" s="11">
-        <v>-68281.5287394958</v>
-      </c>
-      <c r="N26" s="11">
-        <v>0</v>
-      </c>
-      <c r="O26" s="10">
-        <v>-68281.5287394958</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" s="8">
-        <v>45837</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I27" s="10">
-        <v>7507426.3200000003</v>
-      </c>
-      <c r="J27" s="10">
-        <v>1426411</v>
-      </c>
-      <c r="K27" s="11">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11">
-        <v>0</v>
-      </c>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11">
-        <v>0</v>
-      </c>
-      <c r="O27" s="10">
-        <v>8933837.3200000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28" s="8">
-        <v>45837</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="10">
-        <v>0</v>
-      </c>
-      <c r="J28" s="10">
-        <v>0</v>
-      </c>
-      <c r="K28" s="11">
-        <v>0</v>
-      </c>
-      <c r="L28" s="11">
-        <v>0</v>
-      </c>
-      <c r="M28" s="11">
-        <v>-150148.52638655499</v>
-      </c>
-      <c r="N28" s="11">
-        <v>0</v>
-      </c>
-      <c r="O28" s="10">
-        <v>-150148.52638655499</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="E7:E28"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="A18:O18"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="N7:N8"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="A7:A28"/>
-    <mergeCell ref="B7:B28"/>
-    <mergeCell ref="C7:C28"/>
-    <mergeCell ref="D7:D28"/>
     <mergeCell ref="F6:O6"/>
+    <mergeCell ref="A7:A14"/>
+    <mergeCell ref="B7:B14"/>
+    <mergeCell ref="C7:C14"/>
+    <mergeCell ref="D7:D14"/>
+    <mergeCell ref="E7:E14"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/Archivos/Remittance/Remittance_farmatodo.xlsx
+++ b/app/Archivos/Remittance/Remittance_farmatodo.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose-Ricardo.Morales\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unilever-my.sharepoint.com/personal/jose-ricardo_morales_unilever_com/Documents/Cartera/PROYECTOS/Cash App Cross Andina/Python/Unilever_Collect_Digital/app/Archivos/Remittance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{054ECFC4-7BD4-4BE0-A8C1-0D4A55F2CF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E33F5A56-62EE-4C04-9D78-5295930D9EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B7AE75B-2B70-4199-BC30-4D3FD27995FF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8C9C822-248D-4E84-9180-003B98D50675}"/>
   </bookViews>
   <sheets>
-    <sheet name="o17511397" sheetId="2" r:id="rId1"/>
+    <sheet name="o17526606" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" concurrentManualCount="12"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>FARMATODO COLOMBIA, S.A.</t>
   </si>
@@ -61,7 +61,7 @@
     <t>PROSEGUR</t>
   </si>
   <si>
-    <t>‭17-SEP-2025‬</t>
+    <t>‭19-SEP-2025‬</t>
   </si>
   <si>
     <t>COP</t>
@@ -100,40 +100,55 @@
     <t>Total</t>
   </si>
   <si>
-    <t>‭PMP1279547‬</t>
+    <t>‭NCNC-DC04-757790‬</t>
+  </si>
+  <si>
+    <t>Cobro Descuento Apoyo Apertura mes de Agosto (Cerritos, Americas, Palmas)</t>
+  </si>
+  <si>
+    <t>‭NDNC-DC04-757791‬</t>
+  </si>
+  <si>
+    <t>Liquidaciones ventas pos Agosto - Cuidado De La Mama</t>
+  </si>
+  <si>
+    <t>‭NDNC-DC04-757790‬</t>
+  </si>
+  <si>
+    <t>Liquidaciones ventas pos Agosto - Horas De Locura 31 a 1</t>
+  </si>
+  <si>
+    <t>‭NDNC-DC04-757789‬</t>
+  </si>
+  <si>
+    <t>Liquidaciones ventas pos Agosto - Semana Lactancia</t>
+  </si>
+  <si>
+    <t>‭NCNC-DC04-757791‬</t>
+  </si>
+  <si>
+    <t>Ponds Serum solar</t>
+  </si>
+  <si>
+    <t>‭NCNC-DC04-757789‬</t>
+  </si>
+  <si>
+    <t>Negociaciones Unilever</t>
+  </si>
+  <si>
+    <t>‭CNQPMP1279546‬</t>
   </si>
   <si>
     <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA</t>
   </si>
   <si>
-    <t>‭NC-PMP1279547‬</t>
+    <t>‭PMP1279546‬</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1279546‬</t>
   </si>
   <si>
     <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
-  </si>
-  <si>
-    <t>‭NC-PMP1279567‬</t>
-  </si>
-  <si>
-    <t>OC:14007453 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
-  </si>
-  <si>
-    <t>‭PMP1279567‬</t>
-  </si>
-  <si>
-    <t>OC:14007453 UNILEVER ANDINA COLOMBIA LTDA</t>
-  </si>
-  <si>
-    <t>‭NC-PMP1279890‬</t>
-  </si>
-  <si>
-    <t>OC:14007449 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
-  </si>
-  <si>
-    <t>‭PMP1279890‬</t>
-  </si>
-  <si>
-    <t>OC:14007449 UNILEVER ANDINA COLOMBIA LTDA</t>
   </si>
   <si>
     <t xml:space="preserve">                     </t>
@@ -1202,25 +1217,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B890F33-5057-4BCE-BF60-B41F54772D10}">
-  <dimension ref="A1:O18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87BF1E9E-4AB6-456A-86BA-CBA383188509}">
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="24.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.88671875" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="23.109375" customWidth="1"/>
-    <col min="13" max="13" width="28.77734375" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="17.77734375" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="37.21875" customWidth="1"/>
+    <col min="9" max="9" width="24.21875" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" customWidth="1"/>
+    <col min="13" max="13" width="28.33203125" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" customWidth="1"/>
+    <col min="15" max="15" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -1270,13 +1285,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="20">
-        <v>35172</v>
+        <v>35183</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="23">
-        <v>218819138.28</v>
+        <v>829921733.04999995</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>10</v>
@@ -1341,16 +1356,16 @@
         <v>22</v>
       </c>
       <c r="G9" s="8">
-        <v>45895</v>
+        <v>45903</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="10">
-        <v>105934733.18000001</v>
-      </c>
-      <c r="J9" s="10">
-        <v>20127599.300000001</v>
+        <v>-39000000</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
@@ -1365,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="10">
-        <v>126062332.48</v>
+        <v>-39000000</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1378,13 +1393,13 @@
         <v>24</v>
       </c>
       <c r="G10" s="8">
-        <v>45895</v>
+        <v>45903</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="11">
-        <v>0</v>
+      <c r="I10" s="10">
+        <v>10000000</v>
       </c>
       <c r="J10" s="11">
         <v>0</v>
@@ -1395,14 +1410,14 @@
       <c r="L10" s="11">
         <v>0</v>
       </c>
-      <c r="M10" s="10">
-        <v>-2118694.66</v>
+      <c r="M10" s="11">
+        <v>0</v>
       </c>
       <c r="N10" s="11">
         <v>0</v>
       </c>
       <c r="O10" s="10">
-        <v>-2118694.66</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1415,13 +1430,13 @@
         <v>26</v>
       </c>
       <c r="G11" s="8">
-        <v>45895</v>
+        <v>45903</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="11">
-        <v>0</v>
+      <c r="I11" s="10">
+        <v>39000000</v>
       </c>
       <c r="J11" s="11">
         <v>0</v>
@@ -1432,14 +1447,14 @@
       <c r="L11" s="11">
         <v>0</v>
       </c>
-      <c r="M11" s="10">
-        <v>-1565497.97</v>
+      <c r="M11" s="11">
+        <v>0</v>
       </c>
       <c r="N11" s="11">
         <v>0</v>
       </c>
       <c r="O11" s="10">
-        <v>-1565497.97</v>
+        <v>39000000</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1452,16 +1467,16 @@
         <v>28</v>
       </c>
       <c r="G12" s="8">
-        <v>45895</v>
+        <v>45903</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I12" s="10">
-        <v>78274898.359999999</v>
-      </c>
-      <c r="J12" s="10">
-        <v>14872230.689999999</v>
+        <v>70000000</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -1476,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="10">
-        <v>93147129.049999997</v>
+        <v>70000000</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1489,13 +1504,13 @@
         <v>30</v>
       </c>
       <c r="G13" s="8">
-        <v>45896</v>
+        <v>45903</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="11">
-        <v>0</v>
+      <c r="I13" s="10">
+        <v>-10000000</v>
       </c>
       <c r="J13" s="11">
         <v>0</v>
@@ -1506,36 +1521,36 @@
       <c r="L13" s="11">
         <v>0</v>
       </c>
-      <c r="M13" s="10">
-        <v>-50437.48</v>
+      <c r="M13" s="11">
+        <v>0</v>
       </c>
       <c r="N13" s="11">
         <v>0</v>
       </c>
       <c r="O13" s="10">
-        <v>-50437.48</v>
+        <v>-10000000</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="22"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="5" t="s">
         <v>32</v>
       </c>
       <c r="G14" s="8">
-        <v>45896</v>
+        <v>45903</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>33</v>
       </c>
       <c r="I14" s="10">
-        <v>2865150.8</v>
-      </c>
-      <c r="J14" s="10">
-        <v>479156.06</v>
+        <v>-70000000</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -1550,40 +1565,151 @@
         <v>0</v>
       </c>
       <c r="O14" s="10">
-        <v>3344306.86</v>
+        <v>-70000000</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+    <row r="15" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
+      <c r="G15" s="8">
+        <v>45918</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="10">
+        <v>-3400824</v>
+      </c>
+      <c r="J15" s="10">
+        <v>-646156.56000000006</v>
+      </c>
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11">
+        <v>0</v>
+      </c>
+      <c r="N15" s="11">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <v>-4046980.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="8">
+        <v>45895</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="10">
+        <v>712793772.32000005</v>
+      </c>
+      <c r="J16" s="10">
+        <v>135430816.74000001</v>
+      </c>
+      <c r="K16" s="11">
+        <v>0</v>
+      </c>
+      <c r="L16" s="11">
+        <v>0</v>
+      </c>
+      <c r="M16" s="11">
+        <v>0</v>
+      </c>
+      <c r="N16" s="11">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>848224589.05999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="8">
+        <v>45895</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11">
+        <v>0</v>
+      </c>
+      <c r="K17" s="11">
+        <v>0</v>
+      </c>
+      <c r="L17" s="11">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>-14255875.449999999</v>
+      </c>
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
+        <v>-14255875.449999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A21:O21"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="F6:O6"/>
-    <mergeCell ref="A7:A14"/>
-    <mergeCell ref="B7:B14"/>
-    <mergeCell ref="C7:C14"/>
-    <mergeCell ref="D7:D14"/>
-    <mergeCell ref="E7:E14"/>
+    <mergeCell ref="A7:A17"/>
+    <mergeCell ref="B7:B17"/>
+    <mergeCell ref="C7:C17"/>
+    <mergeCell ref="D7:D17"/>
+    <mergeCell ref="E7:E17"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="H7:H8"/>

--- a/app/Archivos/Remittance/Remittance_farmatodo.xlsx
+++ b/app/Archivos/Remittance/Remittance_farmatodo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unilever-my.sharepoint.com/personal/jose-ricardo_morales_unilever_com/Documents/Cartera/PROYECTOS/Cash App Cross Andina/Python/Unilever_Collect_Digital/app/Archivos/Remittance/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose-Ricardo.Morales\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E33F5A56-62EE-4C04-9D78-5295930D9EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2B41D08-7339-443D-B8B6-F1F97E249F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8C9C822-248D-4E84-9180-003B98D50675}"/>
   </bookViews>
@@ -1719,4 +1719,10 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{89db4e91-bad5-4fd0-9ca4-c06485916e3a}" enabled="1" method="Standard" siteId="{f66fae02-5d36-495b-bfe0-78a6ff9f8e6e}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/app/Archivos/Remittance/Remittance_farmatodo.xlsx
+++ b/app/Archivos/Remittance/Remittance_farmatodo.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose-Ricardo.Morales\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2B41D08-7339-443D-B8B6-F1F97E249F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{738B76BD-46F5-412B-8BE8-C4437ABAA6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8C9C822-248D-4E84-9180-003B98D50675}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FCE9160C-AA24-44C7-ADF4-0AB3F30530C5}"/>
   </bookViews>
   <sheets>
-    <sheet name="o17526606" sheetId="2" r:id="rId1"/>
+    <sheet name="o17549176" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>FARMATODO COLOMBIA, S.A.</t>
   </si>
@@ -61,7 +74,7 @@
     <t>PROSEGUR</t>
   </si>
   <si>
-    <t>‭19-SEP-2025‬</t>
+    <t>‭24-SEP-2025‬</t>
   </si>
   <si>
     <t>COP</t>
@@ -100,55 +113,28 @@
     <t>Total</t>
   </si>
   <si>
-    <t>‭NCNC-DC04-757790‬</t>
-  </si>
-  <si>
-    <t>Cobro Descuento Apoyo Apertura mes de Agosto (Cerritos, Americas, Palmas)</t>
-  </si>
-  <si>
-    <t>‭NDNC-DC04-757791‬</t>
-  </si>
-  <si>
-    <t>Liquidaciones ventas pos Agosto - Cuidado De La Mama</t>
-  </si>
-  <si>
-    <t>‭NDNC-DC04-757790‬</t>
-  </si>
-  <si>
-    <t>Liquidaciones ventas pos Agosto - Horas De Locura 31 a 1</t>
-  </si>
-  <si>
-    <t>‭NDNC-DC04-757789‬</t>
-  </si>
-  <si>
-    <t>Liquidaciones ventas pos Agosto - Semana Lactancia</t>
-  </si>
-  <si>
-    <t>‭NCNC-DC04-757791‬</t>
-  </si>
-  <si>
-    <t>Ponds Serum solar</t>
-  </si>
-  <si>
-    <t>‭NCNC-DC04-757789‬</t>
-  </si>
-  <si>
-    <t>Negociaciones Unilever</t>
-  </si>
-  <si>
-    <t>‭CNQPMP1279546‬</t>
-  </si>
-  <si>
-    <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA</t>
-  </si>
-  <si>
-    <t>‭PMP1279546‬</t>
-  </si>
-  <si>
-    <t>‭NC-PMP1279546‬</t>
-  </si>
-  <si>
-    <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+    <t>‭NC100331707‬</t>
+  </si>
+  <si>
+    <t>NOTAS DE CREDITO POR DEVOLUCION 100331707</t>
+  </si>
+  <si>
+    <t>‭PMP1281720‬</t>
+  </si>
+  <si>
+    <t>OC:14007843 UNILEVER ANDINA COLOMBIA LTDA</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1281721‬</t>
+  </si>
+  <si>
+    <t>OC:14007843 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1281720‬</t>
+  </si>
+  <si>
+    <t>‭PMP1281721‬</t>
   </si>
   <si>
     <t xml:space="preserve">                     </t>
@@ -1217,25 +1203,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87BF1E9E-4AB6-456A-86BA-CBA383188509}">
-  <dimension ref="A1:O21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C198F62C-94CB-4B0B-949F-CDA2F9985526}">
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="21.77734375" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="37.21875" customWidth="1"/>
-    <col min="9" max="9" width="24.21875" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" customWidth="1"/>
-    <col min="12" max="12" width="22.6640625" customWidth="1"/>
-    <col min="13" max="13" width="28.33203125" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" customWidth="1"/>
-    <col min="15" max="15" width="17.5546875" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="38.44140625" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="29.21875" customWidth="1"/>
+    <col min="14" max="14" width="16.21875" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -1285,13 +1270,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="20">
-        <v>35183</v>
+        <v>35264</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="23">
-        <v>829921733.04999995</v>
+        <v>38708038.990000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>10</v>
@@ -1356,16 +1341,16 @@
         <v>22</v>
       </c>
       <c r="G9" s="8">
-        <v>45903</v>
+        <v>45922</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="10">
-        <v>-39000000</v>
-      </c>
-      <c r="J9" s="11">
-        <v>0</v>
+        <v>-1226751.24</v>
+      </c>
+      <c r="J9" s="10">
+        <v>-233082.74</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
@@ -1380,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="10">
-        <v>-39000000</v>
+        <v>-1459833.98</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1393,16 +1378,16 @@
         <v>24</v>
       </c>
       <c r="G10" s="8">
-        <v>45903</v>
+        <v>45899</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="J10" s="11">
-        <v>0</v>
+        <v>11788610.039999999</v>
+      </c>
+      <c r="J10" s="10">
+        <v>2239835.91</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -1417,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="10">
-        <v>10000000</v>
+        <v>14028445.949999999</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1430,13 +1415,13 @@
         <v>26</v>
       </c>
       <c r="G11" s="8">
-        <v>45903</v>
+        <v>45899</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="10">
-        <v>39000000</v>
+      <c r="I11" s="11">
+        <v>0</v>
       </c>
       <c r="J11" s="11">
         <v>0</v>
@@ -1447,14 +1432,14 @@
       <c r="L11" s="11">
         <v>0</v>
       </c>
-      <c r="M11" s="11">
-        <v>0</v>
+      <c r="M11" s="10">
+        <v>-450858.11</v>
       </c>
       <c r="N11" s="11">
         <v>0</v>
       </c>
       <c r="O11" s="10">
-        <v>39000000</v>
+        <v>-450858.11</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1467,13 +1452,13 @@
         <v>28</v>
       </c>
       <c r="G12" s="8">
-        <v>45903</v>
+        <v>45899</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="10">
-        <v>70000000</v>
+        <v>27</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0</v>
       </c>
       <c r="J12" s="11">
         <v>0</v>
@@ -1484,36 +1469,36 @@
       <c r="L12" s="11">
         <v>0</v>
       </c>
-      <c r="M12" s="11">
-        <v>0</v>
+      <c r="M12" s="10">
+        <v>-235772.2</v>
       </c>
       <c r="N12" s="11">
         <v>0</v>
       </c>
       <c r="O12" s="10">
-        <v>70000000</v>
+        <v>-235772.2</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="21"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" s="8">
-        <v>45903</v>
+        <v>45899</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I13" s="10">
-        <v>-10000000</v>
-      </c>
-      <c r="J13" s="11">
-        <v>0</v>
+        <v>22542905.32</v>
+      </c>
+      <c r="J13" s="10">
+        <v>4283152.01</v>
       </c>
       <c r="K13" s="11">
         <v>0</v>
@@ -1528,188 +1513,40 @@
         <v>0</v>
       </c>
       <c r="O13" s="10">
-        <v>-10000000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="8">
-        <v>45903</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="10">
-        <v>-70000000</v>
-      </c>
-      <c r="J14" s="11">
-        <v>0</v>
-      </c>
-      <c r="K14" s="11">
-        <v>0</v>
-      </c>
-      <c r="L14" s="11">
-        <v>0</v>
-      </c>
-      <c r="M14" s="11">
-        <v>0</v>
-      </c>
-      <c r="N14" s="11">
-        <v>0</v>
-      </c>
-      <c r="O14" s="10">
-        <v>-70000000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="8">
-        <v>45918</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="10">
-        <v>-3400824</v>
-      </c>
-      <c r="J15" s="10">
-        <v>-646156.56000000006</v>
-      </c>
-      <c r="K15" s="11">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11">
-        <v>0</v>
-      </c>
-      <c r="M15" s="11">
-        <v>0</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10">
-        <v>-4046980.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="8">
-        <v>45895</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="10">
-        <v>712793772.32000005</v>
-      </c>
-      <c r="J16" s="10">
-        <v>135430816.74000001</v>
-      </c>
-      <c r="K16" s="11">
-        <v>0</v>
-      </c>
-      <c r="L16" s="11">
-        <v>0</v>
-      </c>
-      <c r="M16" s="11">
-        <v>0</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0</v>
-      </c>
-      <c r="O16" s="10">
-        <v>848224589.05999994</v>
+        <v>26826057.329999998</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="8">
-        <v>45895</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="11">
-        <v>0</v>
-      </c>
-      <c r="J17" s="11">
-        <v>0</v>
-      </c>
-      <c r="K17" s="11">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11">
-        <v>0</v>
-      </c>
-      <c r="M17" s="10">
-        <v>-14255875.449999999</v>
-      </c>
-      <c r="N17" s="11">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10">
-        <v>-14255875.449999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
+      <c r="A17" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="A17:O17"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="F6:O6"/>
-    <mergeCell ref="A7:A17"/>
-    <mergeCell ref="B7:B17"/>
-    <mergeCell ref="C7:C17"/>
-    <mergeCell ref="D7:D17"/>
-    <mergeCell ref="E7:E17"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E7:E13"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="H7:H8"/>
@@ -1719,10 +1556,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{89db4e91-bad5-4fd0-9ca4-c06485916e3a}" enabled="1" method="Standard" siteId="{f66fae02-5d36-495b-bfe0-78a6ff9f8e6e}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/app/Archivos/Remittance/Remittance_farmatodo.xlsx
+++ b/app/Archivos/Remittance/Remittance_farmatodo.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose-Ricardo.Morales\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{738B76BD-46F5-412B-8BE8-C4437ABAA6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD64230B-F570-497C-9B56-454C17AD2AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FCE9160C-AA24-44C7-ADF4-0AB3F30530C5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F95BF203-43EA-4EE3-A8BD-B1D108775570}"/>
   </bookViews>
   <sheets>
-    <sheet name="o17549176" sheetId="2" r:id="rId1"/>
+    <sheet name="o17561801" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>FARMATODO COLOMBIA, S.A.</t>
   </si>
@@ -71,10 +58,10 @@
     <t>Moneda Pago</t>
   </si>
   <si>
-    <t>PROSEGUR</t>
-  </si>
-  <si>
-    <t>‭24-SEP-2025‬</t>
+    <t>BANCOLOMBIA</t>
+  </si>
+  <si>
+    <t>‭26-SEP-2025‬</t>
   </si>
   <si>
     <t>COP</t>
@@ -113,28 +100,46 @@
     <t>Total</t>
   </si>
   <si>
-    <t>‭NC100331707‬</t>
-  </si>
-  <si>
-    <t>NOTAS DE CREDITO POR DEVOLUCION 100331707</t>
-  </si>
-  <si>
-    <t>‭PMP1281720‬</t>
-  </si>
-  <si>
-    <t>OC:14007843 UNILEVER ANDINA COLOMBIA LTDA</t>
-  </si>
-  <si>
-    <t>‭NC-PMP1281721‬</t>
-  </si>
-  <si>
-    <t>OC:14007843 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
-  </si>
-  <si>
-    <t>‭NC-PMP1281720‬</t>
-  </si>
-  <si>
-    <t>‭PMP1281721‬</t>
+    <t>‭CNQPMP1281718‬</t>
+  </si>
+  <si>
+    <t>OC:14007743 UNILEVER ANDINA COLOMBIA LTDA</t>
+  </si>
+  <si>
+    <t>‭CNQPMP1281717‬</t>
+  </si>
+  <si>
+    <t>OC:14007913 UNILEVER ANDINA COLOMBIA LTDA</t>
+  </si>
+  <si>
+    <t>‭PMP1281718‬</t>
+  </si>
+  <si>
+    <t>‭PMP1281719‬</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1281718‬</t>
+  </si>
+  <si>
+    <t>OC:14007743 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1281717‬</t>
+  </si>
+  <si>
+    <t>OC:14007913 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+  </si>
+  <si>
+    <t>‭PMP1281716‬</t>
+  </si>
+  <si>
+    <t>‭PMP1281717‬</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1281716‬</t>
+  </si>
+  <si>
+    <t>‭NC-PMP1281719‬</t>
   </si>
   <si>
     <t xml:space="preserve">                     </t>
@@ -1203,24 +1208,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C198F62C-94CB-4B0B-949F-CDA2F9985526}">
-  <dimension ref="A1:O17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F337251A-38D7-4C1B-B835-8CFDDA285065}">
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.21875" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" customWidth="1"/>
-    <col min="8" max="8" width="38.44140625" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" customWidth="1"/>
-    <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="29.21875" customWidth="1"/>
-    <col min="14" max="14" width="16.21875" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" customWidth="1"/>
+    <col min="8" max="8" width="36.88671875" customWidth="1"/>
+    <col min="9" max="9" width="23.88671875" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" customWidth="1"/>
+    <col min="13" max="13" width="28" customWidth="1"/>
+    <col min="14" max="14" width="15.5546875" customWidth="1"/>
+    <col min="15" max="15" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -1270,13 +1276,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="20">
-        <v>35264</v>
+        <v>1000165002</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="23">
-        <v>38708038.990000002</v>
+        <v>843406905.77999997</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>10</v>
@@ -1341,16 +1347,16 @@
         <v>22</v>
       </c>
       <c r="G9" s="8">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="10">
-        <v>-1226751.24</v>
+        <v>-1515732</v>
       </c>
       <c r="J9" s="10">
-        <v>-233082.74</v>
+        <v>-287989.08</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
@@ -1365,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="10">
-        <v>-1459833.98</v>
+        <v>-1803721.08</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1378,16 +1384,16 @@
         <v>24</v>
       </c>
       <c r="G10" s="8">
-        <v>45899</v>
+        <v>45926</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="10">
-        <v>11788610.039999999</v>
+        <v>-2841792.92</v>
       </c>
       <c r="J10" s="10">
-        <v>2239835.91</v>
+        <v>-539940.65</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -1402,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="10">
-        <v>14028445.949999999</v>
+        <v>-3381733.57</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1418,13 +1424,13 @@
         <v>45899</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="11">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I11" s="10">
+        <v>227106246.28</v>
+      </c>
+      <c r="J11" s="10">
+        <v>43150186.789999999</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
@@ -1432,14 +1438,14 @@
       <c r="L11" s="11">
         <v>0</v>
       </c>
-      <c r="M11" s="10">
-        <v>-450858.11</v>
+      <c r="M11" s="11">
+        <v>0</v>
       </c>
       <c r="N11" s="11">
         <v>0</v>
       </c>
       <c r="O11" s="10">
-        <v>-450858.11</v>
+        <v>270256433.06999999</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1449,19 +1455,19 @@
       <c r="D12" s="24"/>
       <c r="E12" s="21"/>
       <c r="F12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="8">
         <v>45899</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="11">
-        <v>0</v>
-      </c>
-      <c r="J12" s="11">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I12" s="10">
+        <v>60407580.700000003</v>
+      </c>
+      <c r="J12" s="10">
+        <v>11477440.33</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -1469,84 +1475,269 @@
       <c r="L12" s="11">
         <v>0</v>
       </c>
-      <c r="M12" s="10">
-        <v>-235772.2</v>
+      <c r="M12" s="11">
+        <v>0</v>
       </c>
       <c r="N12" s="11">
         <v>0</v>
       </c>
       <c r="O12" s="10">
-        <v>-235772.2</v>
+        <v>71885021.030000001</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="22"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="21"/>
       <c r="F13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" s="8">
         <v>45899</v>
       </c>
       <c r="H13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11">
+        <v>0</v>
+      </c>
+      <c r="L13" s="11">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>-4542124.93</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10">
+        <v>-4542124.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="8">
+        <v>45899</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11">
+        <v>0</v>
+      </c>
+      <c r="M14" s="10">
+        <v>-7393016.3099999996</v>
+      </c>
+      <c r="N14" s="11">
+        <v>0</v>
+      </c>
+      <c r="O14" s="10">
+        <v>-7393016.3099999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="8">
+        <v>45899</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="10">
-        <v>22542905.32</v>
-      </c>
-      <c r="J13" s="10">
-        <v>4283152.01</v>
-      </c>
-      <c r="K13" s="11">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11">
-        <v>0</v>
-      </c>
-      <c r="M13" s="11">
-        <v>0</v>
-      </c>
-      <c r="N13" s="11">
-        <v>0</v>
-      </c>
-      <c r="O13" s="10">
-        <v>26826057.329999998</v>
+      <c r="I15" s="10">
+        <v>68127973.420000002</v>
+      </c>
+      <c r="J15" s="10">
+        <v>12944314.949999999</v>
+      </c>
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11">
+        <v>0</v>
+      </c>
+      <c r="N15" s="11">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <v>81072288.370000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="8">
+        <v>45899</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="10">
+        <v>369650815.36000001</v>
+      </c>
+      <c r="J16" s="10">
+        <v>70233654.920000002</v>
+      </c>
+      <c r="K16" s="11">
+        <v>0</v>
+      </c>
+      <c r="L16" s="11">
+        <v>0</v>
+      </c>
+      <c r="M16" s="11">
+        <v>0</v>
+      </c>
+      <c r="N16" s="11">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>439884470.27999997</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="8">
+        <v>45899</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11">
+        <v>0</v>
+      </c>
+      <c r="K17" s="11">
+        <v>0</v>
+      </c>
+      <c r="L17" s="11">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>-1362559.47</v>
+      </c>
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
+        <v>-1362559.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="8">
+        <v>45899</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0</v>
+      </c>
+      <c r="J18" s="11">
+        <v>0</v>
+      </c>
+      <c r="K18" s="11">
+        <v>0</v>
+      </c>
+      <c r="L18" s="11">
+        <v>0</v>
+      </c>
+      <c r="M18" s="10">
+        <v>-1208151.6100000001</v>
+      </c>
+      <c r="N18" s="11">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10">
+        <v>-1208151.6100000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A22:O22"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="F6:O6"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="C7:C13"/>
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E7:E13"/>
+    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="B7:B18"/>
+    <mergeCell ref="C7:C18"/>
+    <mergeCell ref="D7:D18"/>
+    <mergeCell ref="E7:E18"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="H7:H8"/>
